--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="584">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,6 +896,12 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="67875-5"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -5627,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5666,7 +5672,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5687,10 +5693,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5701,10 +5707,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5730,16 +5736,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5788,7 +5794,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5809,10 +5815,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5823,10 +5829,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5849,19 +5855,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5910,7 +5916,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5925,19 +5931,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5945,10 +5951,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5971,16 +5977,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6030,7 +6036,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6054,10 +6060,10 @@
         <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6065,14 +6071,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6091,19 +6097,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6152,7 +6158,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6167,19 +6173,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6187,14 +6193,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6213,19 +6219,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6274,7 +6280,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6289,19 +6295,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6309,10 +6315,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6338,13 +6344,13 @@
         <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6394,7 +6400,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6415,13 +6421,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6429,10 +6435,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6455,17 +6461,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6514,7 +6520,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6529,19 +6535,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6549,10 +6555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6578,16 +6584,16 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6636,7 +6642,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6645,7 +6651,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6654,27 +6660,27 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6789,10 +6795,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6909,10 +6915,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6991,10 +6997,10 @@
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7015,10 +7021,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7029,13 +7035,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
@@ -7098,7 +7104,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7116,7 +7122,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7137,10 +7143,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7151,10 +7157,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7269,10 +7275,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7389,10 +7395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7418,16 +7424,16 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7437,7 +7443,7 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>82</v>
@@ -7476,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7497,10 +7503,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7511,10 +7517,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7540,13 +7546,13 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7596,7 +7602,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7617,10 +7623,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7631,10 +7637,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7660,14 +7666,14 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7716,7 +7722,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7737,10 +7743,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7751,10 +7757,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7780,14 +7786,14 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7836,7 +7842,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7857,10 +7863,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7871,10 +7877,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7897,19 +7903,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7958,7 +7964,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7979,10 +7985,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7993,13 +7999,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
@@ -8062,7 +8068,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8080,7 +8086,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8101,10 +8107,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8115,10 +8121,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8233,10 +8239,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8353,10 +8359,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8382,16 +8388,16 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8401,7 +8407,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8440,7 +8446,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8461,10 +8467,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8475,10 +8481,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8504,13 +8510,13 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8560,7 +8566,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8581,10 +8587,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8595,10 +8601,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8624,14 +8630,14 @@
         <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8680,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8701,10 +8707,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8715,10 +8721,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,14 +8750,14 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8800,7 +8806,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8821,10 +8827,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8835,10 +8841,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,19 +8867,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8922,7 +8928,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8943,10 +8949,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8957,10 +8963,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8986,16 +8992,16 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9044,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9065,10 +9071,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9079,10 +9085,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9108,16 +9114,16 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9145,10 +9151,10 @@
         <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9166,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9175,7 +9181,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9190,7 +9196,7 @@
         <v>192</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9201,14 +9207,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9230,16 +9236,16 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9267,10 +9273,10 @@
         <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9288,7 +9294,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9306,27 +9312,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9349,19 +9355,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9410,7 +9416,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9431,10 +9437,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9445,10 +9451,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9474,13 +9480,13 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9509,10 +9515,10 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9530,7 +9536,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9548,27 +9554,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9594,16 +9600,16 @@
         <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9631,10 +9637,10 @@
         <v>159</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9652,7 +9658,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9673,10 +9679,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9687,10 +9693,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9713,16 +9719,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9772,7 +9778,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9790,27 +9796,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9833,16 +9839,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9892,7 +9898,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9910,27 +9916,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9953,19 +9959,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10014,7 +10020,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10026,7 +10032,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10035,10 +10041,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10049,10 +10055,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10167,10 +10173,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10287,14 +10293,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10316,10 +10322,10 @@
         <v>114</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>117</v>
@@ -10374,7 +10380,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10409,10 +10415,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10435,13 +10441,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10492,7 +10498,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10501,7 +10507,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10513,10 +10519,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10527,10 +10533,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10553,13 +10559,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10610,7 +10616,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10619,7 +10625,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10631,10 +10637,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10645,10 +10651,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10674,16 +10680,16 @@
         <v>243</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10711,10 +10717,10 @@
         <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10732,7 +10738,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10750,13 +10756,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10767,10 +10773,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10796,16 +10802,16 @@
         <v>243</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10833,10 +10839,10 @@
         <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10854,7 +10860,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10872,13 +10878,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10889,10 +10895,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10915,17 +10921,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10974,7 +10980,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10998,7 +11004,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11009,10 +11015,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11038,10 +11044,10 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11092,7 +11098,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11113,10 +11119,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11127,10 +11133,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11153,16 +11159,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11212,7 +11218,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11233,10 +11239,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11247,10 +11253,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11273,16 +11279,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11332,7 +11338,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11353,10 +11359,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11367,10 +11373,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11393,19 +11399,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11454,7 +11460,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11475,10 +11481,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11489,10 +11495,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11607,10 +11613,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11727,14 +11733,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11756,10 +11762,10 @@
         <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>117</v>
@@ -11814,7 +11820,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11849,10 +11855,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11878,13 +11884,13 @@
         <v>243</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>264</v>
@@ -11936,7 +11942,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -11954,7 +11960,7 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>269</v>
@@ -11971,10 +11977,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11997,19 +12003,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12058,7 +12064,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12076,27 +12082,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12122,16 +12128,16 @@
         <v>243</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12159,10 +12165,10 @@
         <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12180,7 +12186,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12189,7 +12195,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12204,7 +12210,7 @@
         <v>192</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12215,14 +12221,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12244,16 +12250,16 @@
         <v>243</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12281,10 +12287,10 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12302,7 +12308,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12320,27 +12326,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12366,16 +12372,16 @@
         <v>83</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12424,7 +12430,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12445,10 +12451,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
+++ b/StructureDefinition-mii-pr-sdd-beschaeftigungsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
